--- a/forms/contact/screening_camp-create.xlsx
+++ b/forms/contact/screening_camp-create.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,8 +491,6 @@
           <t>NO_LABEL</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>field-list</t>
@@ -503,10 +501,6 @@
           <t>false()</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,14 +518,6 @@
           <t>NO_LABEL</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -549,14 +535,6 @@
           <t>NO_LABEL</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -574,14 +552,6 @@
           <t>NO_LABEL</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -599,14 +569,6 @@
           <t>NO_LABEL</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -614,16 +576,6 @@
           <t>end group</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -631,16 +583,6 @@
           <t>end group</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -655,21 +597,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NO_LABEL</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>Screening Camp</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -687,13 +622,6 @@
           <t>NO_LABEL</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>screening_camp</t>
@@ -716,18 +644,11 @@
           <t>Camp Name</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -745,18 +666,11 @@
           <t>Location</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -774,11 +688,6 @@
           <t>Contact Number</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>true()</t>
@@ -789,7 +698,6 @@
           <t>Please enter a valid phone number.</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -807,18 +715,11 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>multiline</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -826,16 +727,6 @@
           <t>end group</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
